--- a/Отчёт/MO4.xlsx
+++ b/Отчёт/MO4.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Maksim\source\repos\MaxArt-Term6MO\Отчёт\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AD45332-C523-421E-AAB0-8ECEDD8B4CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED8D7CD8-BAA0-41C6-A35F-68CAD389B5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="165" yWindow="2220" windowWidth="16785" windowHeight="12855" xr2:uid="{1917DAC0-F603-47D0-A7E9-3E186B262FEF}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="26">
   <si>
     <t>V=</t>
   </si>
@@ -87,13 +87,43 @@
   </si>
   <si>
     <t>y:</t>
+  </si>
+  <si>
+    <t>alg1</t>
+  </si>
+  <si>
+    <t>alg2</t>
+  </si>
+  <si>
+    <t>alg3</t>
+  </si>
+  <si>
+    <t>m=20</t>
+  </si>
+  <si>
+    <t>m=10</t>
+  </si>
+  <si>
+    <t>m=50</t>
+  </si>
+  <si>
+    <t>Count_use_function:</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>algorithm_2:</t>
+  </si>
+  <si>
+    <t>m=200</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,6 +131,19 @@
       <family val="2"/>
       <charset val="204"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+      <charset val="204"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -117,7 +160,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -154,11 +197,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -175,6 +246,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -510,14 +590,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F17CDDA9-E507-4528-B488-12B02393C974}">
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:AA40"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="6" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -529,7 +610,7 @@
       </c>
       <c r="D1" s="2"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -544,7 +625,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -559,7 +640,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>10</v>
       </c>
@@ -574,7 +655,7 @@
         <v>1E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -594,7 +675,7 @@
         <v>0.999</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
@@ -619,7 +700,7 @@
         <v>276306.75726667151</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>3</v>
       </c>
@@ -644,7 +725,7 @@
         <v>27631017.658188552</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>4</v>
       </c>
@@ -669,115 +750,758 @@
         <v>2763102124.9316497</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:16" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>12</v>
       </c>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="N11" t="s">
+        <v>14</v>
+      </c>
+      <c r="O11" t="s">
+        <v>15</v>
+      </c>
+      <c r="P11" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>1</v>
       </c>
       <c r="B12" s="6">
         <v>0.95</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="M12" s="9">
+        <v>64377</v>
+      </c>
+      <c r="N12">
+        <v>-8.8959399999999995</v>
+      </c>
+      <c r="O12">
+        <v>-1.10724</v>
+      </c>
+      <c r="P12">
+        <v>-11.7171</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B13" s="1">
         <v>119828</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="1">
+        <v>-11.6486</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H13" s="1">
+        <v>-6.4081599999999996</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="1">
+        <v>-6.4049899999999997</v>
+      </c>
+      <c r="M13" s="9">
+        <v>92103</v>
+      </c>
+      <c r="N13">
+        <v>-8.8847699999999996</v>
+      </c>
+      <c r="O13">
+        <v>-1.1448</v>
+      </c>
+      <c r="P13">
+        <v>-11.7089</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B14" s="1">
-        <v>9.9486199999999997E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-11.7172</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F14" s="1">
+        <v>-8.8984699999999997</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="1">
+        <v>-2.0091000000000001</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="1">
+        <v>-2.0299999999999998</v>
+      </c>
+      <c r="M14" s="9">
+        <v>119828</v>
+      </c>
+      <c r="N14">
+        <v>-8.9062400000000004</v>
+      </c>
+      <c r="O14">
+        <v>-1.1182300000000001</v>
+      </c>
+      <c r="P14">
+        <v>-11.714399999999999</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B15" s="1">
-        <v>9.9446100000000008</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+        <v>-8.8926800000000004</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="1">
+        <v>-1.0179800000000001</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="1">
+        <v>-4.0002800000000001</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J15" s="1">
+        <v>-4.0051899999999998</v>
+      </c>
+      <c r="M15" s="9">
+        <v>184205</v>
+      </c>
+      <c r="N15">
+        <v>-8.8794900000000005</v>
+      </c>
+      <c r="O15">
+        <v>-1.12982</v>
+      </c>
+      <c r="P15">
+        <v>-11.714499999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B16" s="1">
-        <v>-9.9554600000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-1.1058699999999999</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F16" s="1">
+        <v>1005</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1236</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="1">
+        <v>1211</v>
+      </c>
+      <c r="M16" s="9">
+        <v>276307</v>
+      </c>
+      <c r="N16">
+        <v>-8.8854799999999994</v>
+      </c>
+      <c r="O16">
+        <v>-1.0947</v>
+      </c>
+      <c r="P16">
+        <v>-11.7149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E17" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B18" s="1">
         <v>11982928</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="1">
+        <v>-11.242599999999999</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1">
+        <v>-11.7172</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J18" s="1">
+        <v>-11.7102</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B19" s="1">
-        <v>9.8737000000000005E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-11.7174</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F19" s="1">
+        <v>-8.8308199999999992</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H19" s="1">
+        <v>-8.8938699999999997</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J19" s="1">
+        <v>-8.8776600000000006</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B20" s="1">
-        <v>9.99878</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-8.88781</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1">
+        <v>-1.3925700000000001</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="1">
+        <v>-1.10731</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J20" s="1">
+        <v>-1.0860399999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B21" s="1">
-        <v>-9.99892</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-1.1099000000000001</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F21" s="1">
+        <v>2005</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H21" s="1">
+        <v>2442</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="1">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E22" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E23" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F23" s="1">
+        <v>-11.715299999999999</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23" s="1">
+        <v>-6.4081999999999999</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J23" s="1">
+        <v>-6.4076899999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="1">
+        <v>-8.9059699999999999</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="1">
+        <v>-2.0080499999999999</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J24" s="1">
+        <v>-2.01579</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B25" s="1">
         <v>1198292915</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F25" s="1">
+        <v>-1.1045700000000001</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="1">
+        <v>-3.99905</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="J25" s="1">
+        <v>-4.0028899999999998</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B26" s="1">
-        <v>9.8722199999999996E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-11.7174</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F26" s="1">
+        <v>5005</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6036</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="1">
+        <v>6018</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B27" s="1">
-        <v>9.9998299999999993</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+        <v>-8.8901699999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B28" s="1">
-        <v>-9.9998299999999993</v>
+        <v>-1.11066</v>
+      </c>
+      <c r="J28"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J29"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J30"/>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J31"/>
+    </row>
+    <row r="35" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="F35" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G35" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="L35" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="M35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q35" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R35" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="T35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="36" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="H36" s="1">
+        <v>1005</v>
+      </c>
+      <c r="I36" s="1">
+        <v>-8.8984699999999997</v>
+      </c>
+      <c r="J36" s="1">
+        <v>-1.0179800000000001</v>
+      </c>
+      <c r="K36" s="1">
+        <v>-11.6486</v>
+      </c>
+      <c r="L36" s="1"/>
+      <c r="M36" s="1">
+        <v>2005</v>
+      </c>
+      <c r="N36" s="1">
+        <v>-8.8308199999999992</v>
+      </c>
+      <c r="O36" s="1">
+        <v>-1.3925700000000001</v>
+      </c>
+      <c r="P36" s="1">
+        <v>-11.242599999999999</v>
+      </c>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1">
+        <v>5005</v>
+      </c>
+      <c r="S36" s="1">
+        <v>-8.9059699999999999</v>
+      </c>
+      <c r="T36" s="1">
+        <v>-1.1045700000000001</v>
+      </c>
+      <c r="U36" s="1">
+        <v>-11.715299999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="F37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q37" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R37" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S37" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="T37" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U37" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="V37" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="W37" t="s">
+        <v>24</v>
+      </c>
+      <c r="X37" t="s">
+        <v>13</v>
+      </c>
+      <c r="Y37" t="s">
+        <v>14</v>
+      </c>
+      <c r="Z37" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA37" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="38" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="H38" s="1">
+        <v>1236</v>
+      </c>
+      <c r="I38" s="1">
+        <v>-2.0091000000000001</v>
+      </c>
+      <c r="J38" s="1">
+        <v>-4.0002800000000001</v>
+      </c>
+      <c r="K38" s="1">
+        <v>-6.4081599999999996</v>
+      </c>
+      <c r="L38" s="1"/>
+      <c r="M38" s="1">
+        <v>2442</v>
+      </c>
+      <c r="N38" s="1">
+        <v>-8.8938699999999997</v>
+      </c>
+      <c r="O38" s="1">
+        <v>-1.10731</v>
+      </c>
+      <c r="P38" s="1">
+        <v>-11.7172</v>
+      </c>
+      <c r="Q38" s="1"/>
+      <c r="R38" s="1">
+        <v>6036</v>
+      </c>
+      <c r="S38" s="1">
+        <v>-2.0080499999999999</v>
+      </c>
+      <c r="T38" s="1">
+        <v>-3.99905</v>
+      </c>
+      <c r="U38" s="1">
+        <v>-6.4081999999999999</v>
+      </c>
+      <c r="X38">
+        <v>-11.715999999999999</v>
+      </c>
+      <c r="Y38">
+        <v>-8.9015000000000004</v>
+      </c>
+      <c r="Z38">
+        <v>-1.11561</v>
+      </c>
+      <c r="AA38">
+        <v>4336</v>
+      </c>
+    </row>
+    <row r="39" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="F39" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L39" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q39" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="S39" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="T39" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="U39" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="40" spans="6:27" x14ac:dyDescent="0.25">
+      <c r="H40" s="1">
+        <v>1211</v>
+      </c>
+      <c r="I40" s="1">
+        <v>-2.0299999999999998</v>
+      </c>
+      <c r="J40" s="1">
+        <v>-4.0051899999999998</v>
+      </c>
+      <c r="K40" s="1">
+        <v>-6.4049899999999997</v>
+      </c>
+      <c r="L40" s="1"/>
+      <c r="M40" s="1">
+        <v>2411</v>
+      </c>
+      <c r="N40" s="1">
+        <v>-8.8776600000000006</v>
+      </c>
+      <c r="O40" s="1">
+        <v>-1.0860399999999999</v>
+      </c>
+      <c r="P40" s="1">
+        <v>-11.7102</v>
+      </c>
+      <c r="Q40" s="1"/>
+      <c r="R40" s="1">
+        <v>6018</v>
+      </c>
+      <c r="S40" s="1">
+        <v>-2.01579</v>
+      </c>
+      <c r="T40" s="1">
+        <v>-4.0028899999999998</v>
+      </c>
+      <c r="U40" s="1">
+        <v>-6.4076899999999997</v>
       </c>
     </row>
   </sheetData>
